--- a/excel-files/QUEZON CITY/STO. CRISTO ES.xlsx
+++ b/excel-files/QUEZON CITY/STO. CRISTO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B9B1871-EC03-4118-8703-CA0F86DE16C6}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7C2367-919E-48C7-B5F3-8F4AB11B8C62}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5440,8 +5440,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E31:E33 E22:E29 E14:E19 E8:E12 E2:E6 E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E34:E39 E21" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5456,7 +5456,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13444,186 +13444,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
@@ -13641,8 +13461,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13660,7 +13480,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -21917,186 +21737,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22114,8 +21754,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/QUEZON CITY/STO. CRISTO ES.xlsx
+++ b/excel-files/QUEZON CITY/STO. CRISTO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7C2367-919E-48C7-B5F3-8F4AB11B8C62}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C770185-68C1-5C4F-9307-BA90EDB26C03}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="93">
   <si>
     <t>Grade Level</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Reading and Literacy</t>
-  </si>
-  <si>
-    <t>RO</t>
   </si>
   <si>
     <t>Language</t>
@@ -315,12 +312,18 @@
   <si>
     <t>Arts</t>
   </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1832,13 +1835,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1862,6 +1858,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2940,13 +2943,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2983,6 +2979,13 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3025,7 +3028,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3042,7 +3045,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3098,7 +3101,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3471,17 +3474,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3507,7 +3510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3521,10 +3524,10 @@
         <v>303</v>
       </c>
       <c r="E2" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
@@ -3535,12 +3538,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
         <v>179</v>
@@ -3552,7 +3555,7 @@
         <v>2025</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
@@ -3563,12 +3566,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>179</v>
@@ -3580,7 +3583,7 @@
         <v>2024</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
@@ -3591,12 +3594,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>179</v>
@@ -3605,10 +3608,10 @@
         <v>303</v>
       </c>
       <c r="E5" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
@@ -3619,12 +3622,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -3639,237 +3642,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>221</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <v>221</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>221</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <v>221</v>
+      </c>
+      <c r="D11" s="1">
+        <v>273</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C12" s="1">
+        <v>221</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>175</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C15" s="1">
+        <v>175</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="1">
+        <v>175</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C17" s="1">
+        <v>175</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="C18" s="1">
+        <v>175</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C19" s="1">
+        <v>175</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3879,15 +3910,15 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D21" s="1">
         <v>98</v>
@@ -3896,26 +3927,26 @@
         <v>2024</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D22" s="1">
         <v>260</v>
@@ -3924,7 +3955,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3932,18 +3963,18 @@
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D23" s="1">
         <v>260</v>
@@ -3952,7 +3983,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3960,18 +3991,18 @@
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D24" s="1">
         <v>260</v>
@@ -3980,7 +4011,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3988,18 +4019,18 @@
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D25" s="1">
         <v>260</v>
@@ -4008,7 +4039,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
@@ -4016,18 +4047,18 @@
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D26" s="1">
         <v>260</v>
@@ -4036,7 +4067,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
@@ -4044,18 +4075,18 @@
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D27" s="1">
         <v>260</v>
@@ -4064,7 +4095,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
@@ -4072,50 +4103,60 @@
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="1">
+        <v>237</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="1">
+        <v>237</v>
+      </c>
+      <c r="D29" s="1">
+        <v>260</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4125,92 +4166,106 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="C31" s="1">
+        <v>199</v>
+      </c>
+      <c r="D31" s="1">
+        <v>250</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C32" s="1">
+        <v>199</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C33" s="1">
+        <v>199</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C34" s="1">
+        <v>199</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1">
         <v>199</v>
@@ -4222,7 +4277,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4233,87 +4288,113 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="C36" s="1">
+        <v>199</v>
+      </c>
+      <c r="D36" s="1">
+        <v>250</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="1">
+        <v>199</v>
+      </c>
+      <c r="D37" s="1">
+        <v>250</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="1">
+        <v>199</v>
+      </c>
+      <c r="D38" s="1">
+        <v>250</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="1">
+        <v>199</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4323,187 +4404,205 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="C41" s="1">
+        <v>214</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C42" s="1">
+        <v>214</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C43" s="1">
+        <v>214</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C44" s="1">
+        <v>214</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C45" s="1">
+        <v>214</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C46" s="1">
+        <v>214</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="C47" s="1">
+        <v>214</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="C48" s="1">
+        <v>214</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C49" s="1">
+        <v>214</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4513,12 +4612,12 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4533,12 +4632,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4553,12 +4652,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
@@ -4573,12 +4672,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -4593,12 +4692,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -4613,12 +4712,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4633,12 +4732,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
@@ -4653,12 +4752,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
@@ -4673,12 +4772,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -4693,7 +4792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4703,12 +4802,12 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4723,12 +4822,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4743,12 +4842,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -4763,12 +4862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
@@ -4783,12 +4882,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -4803,12 +4902,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4823,12 +4922,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
@@ -4843,12 +4942,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -4863,12 +4962,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -4883,7 +4982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4893,12 +4992,12 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4913,12 +5012,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4933,12 +5032,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
@@ -4953,12 +5052,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
@@ -4973,12 +5072,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -4993,12 +5092,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5013,12 +5112,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -5033,12 +5132,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
@@ -5053,12 +5152,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
@@ -5073,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5083,12 +5182,12 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5103,12 +5202,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5123,12 +5222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
@@ -5143,12 +5242,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
@@ -5163,12 +5262,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -5183,12 +5282,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5203,12 +5302,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -5223,12 +5322,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
@@ -5243,12 +5342,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
@@ -5263,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5273,12 +5372,12 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B91" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -5293,12 +5392,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5313,12 +5412,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5333,12 +5432,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -5353,12 +5452,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -5373,12 +5472,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -5393,12 +5492,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5413,12 +5512,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5440,10 +5539,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E31:E33 E22:E29 E14:E19 E8:E12 E2:E6 E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E34:E39 E21" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E8:E12 E2:E6 E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F91:F98 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5457,37 +5556,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -5495,7 +5594,7 @@
       <c r="H1" s="42"/>
       <c r="I1" s="42"/>
       <c r="J1" s="43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -5503,7 +5602,7 @@
       <c r="N1" s="43"/>
       <c r="O1" s="43"/>
       <c r="P1" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
@@ -5511,7 +5610,7 @@
       <c r="T1" s="44"/>
       <c r="U1" s="44"/>
       <c r="V1" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W1" s="45"/>
       <c r="X1" s="45"/>
@@ -5519,7 +5618,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5530,81 +5629,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="O2" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="R2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="T2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="U2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="V2" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="W2" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="X2" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Z2" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="AA2" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AA2" s="26" t="s">
+    </row>
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="39" t="s">
-        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -5669,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5681,7 +5780,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5750,12 +5849,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -5819,12 +5918,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -5888,12 +5987,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -5957,12 +6056,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -6026,12 +6125,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6095,12 +6194,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6164,12 +6263,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6233,7 +6332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6246,7 +6345,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6315,12 +6414,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -6384,12 +6483,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -6453,12 +6552,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -6522,12 +6621,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -6591,12 +6690,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -6660,12 +6759,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -6729,12 +6828,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -6798,7 +6897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6812,7 +6911,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6881,12 +6980,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -6950,12 +7049,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -7019,12 +7118,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -7088,12 +7187,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -7157,12 +7256,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -7226,12 +7325,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7295,12 +7394,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7364,12 +7463,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -7433,7 +7532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7447,12 +7546,12 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7516,12 +7615,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7585,12 +7684,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -7654,12 +7753,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -7723,12 +7822,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="5">
@@ -7792,12 +7891,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -7861,12 +7960,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -7930,12 +8029,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="5">
@@ -7999,12 +8098,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -8068,7 +8167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8082,12 +8181,12 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -8151,12 +8250,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8220,12 +8319,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -8289,12 +8388,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -8358,12 +8457,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -8427,12 +8526,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8496,12 +8595,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="5">
@@ -8565,12 +8664,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -8634,12 +8733,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -8703,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8717,12 +8816,12 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8786,12 +8885,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -8855,12 +8954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -8924,12 +9023,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -8993,12 +9092,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -9062,12 +9161,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9131,12 +9230,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -9200,12 +9299,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -9269,12 +9368,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="5">
@@ -9338,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9352,12 +9451,12 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9421,12 +9520,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9490,12 +9589,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="12">
@@ -9559,12 +9658,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="12">
@@ -9628,12 +9727,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -9697,12 +9796,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -9766,12 +9865,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -9835,12 +9934,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -9904,12 +10003,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -9973,7 +10072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9987,12 +10086,12 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10056,12 +10155,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10125,12 +10224,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -10194,12 +10293,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="12">
@@ -10263,12 +10362,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10332,12 +10431,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10401,12 +10500,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -10470,12 +10569,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10539,12 +10638,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -10608,7 +10707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10622,12 +10721,12 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10691,12 +10790,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -10760,12 +10859,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -10829,12 +10928,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -10898,12 +10997,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -10967,12 +11066,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11036,12 +11135,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -11105,12 +11204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11174,12 +11273,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -11243,7 +11342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11257,12 +11356,12 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11326,12 +11425,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11395,12 +11494,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -11464,12 +11563,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -11533,12 +11632,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -11602,12 +11701,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -11671,12 +11770,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -11740,12 +11839,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -11809,12 +11908,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -11878,7 +11977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11892,12 +11991,12 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -11961,12 +12060,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -12030,12 +12129,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12099,12 +12198,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12168,12 +12267,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12237,12 +12336,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12306,12 +12405,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12375,12 +12474,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -12444,7 +12543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12455,7 +12554,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12517,7 +12616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12579,7 +12678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12641,7 +12740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12703,7 +12802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12765,7 +12864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12827,7 +12926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12889,7 +12988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12951,7 +13050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13013,7 +13112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13075,7 +13174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13137,7 +13236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13199,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13261,7 +13360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13323,7 +13422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13385,7 +13484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13481,37 +13580,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -13519,7 +13618,7 @@
       <c r="H1" s="42"/>
       <c r="I1" s="42"/>
       <c r="J1" s="43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -13527,7 +13626,7 @@
       <c r="N1" s="43"/>
       <c r="O1" s="43"/>
       <c r="P1" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
@@ -13535,7 +13634,7 @@
       <c r="T1" s="44"/>
       <c r="U1" s="44"/>
       <c r="V1" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W1" s="45"/>
       <c r="X1" s="45"/>
@@ -13543,7 +13642,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13554,79 +13653,79 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="O2" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="R2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="T2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="U2" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="V2" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="W2" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="X2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Z2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="AA2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="AA2" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13695,12 +13794,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5">
@@ -13764,12 +13863,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5">
@@ -13833,12 +13932,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -13902,12 +14001,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -13971,12 +14070,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14040,12 +14139,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14109,12 +14208,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14178,8 +14277,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14248,12 +14347,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="5">
@@ -14317,12 +14416,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5">
@@ -14386,12 +14485,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -14455,12 +14554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -14524,12 +14623,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14593,12 +14692,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -14662,12 +14761,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -14731,8 +14830,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14801,12 +14900,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="5">
@@ -14870,12 +14969,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="5">
@@ -14939,12 +15038,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15008,12 +15107,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -15077,12 +15176,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -15146,12 +15245,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15215,12 +15314,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15284,12 +15383,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15353,13 +15452,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15423,12 +15522,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15492,12 +15591,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -15561,12 +15660,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -15630,12 +15729,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -15699,12 +15798,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -15768,12 +15867,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15837,12 +15936,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -15906,12 +16005,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -15975,12 +16074,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16044,12 +16143,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16113,13 +16212,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16183,12 +16282,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16252,12 +16351,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -16321,12 +16420,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -16390,12 +16489,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -16459,12 +16558,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -16528,12 +16627,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16597,12 +16696,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16666,12 +16765,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -16735,12 +16834,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16804,12 +16903,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -16873,13 +16972,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -16943,12 +17042,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -17012,12 +17111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -17081,12 +17180,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -17150,12 +17249,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -17219,12 +17318,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -17288,12 +17387,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17357,12 +17456,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17426,12 +17525,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="5">
@@ -17495,12 +17594,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17564,12 +17663,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17633,13 +17732,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -17703,12 +17802,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -17772,12 +17871,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -17841,12 +17940,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -17910,12 +18009,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -17979,12 +18078,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18048,12 +18147,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18117,12 +18216,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18186,12 +18285,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -18255,12 +18354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18324,12 +18423,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18393,13 +18492,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18463,12 +18562,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -18532,12 +18631,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -18601,12 +18700,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -18670,12 +18769,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -18739,12 +18838,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -18808,12 +18907,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -18877,12 +18976,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -18946,12 +19045,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19015,12 +19114,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19084,12 +19183,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19153,13 +19252,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19223,12 +19322,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19292,12 +19391,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -19361,12 +19460,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -19430,12 +19529,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -19499,12 +19598,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -19568,12 +19667,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19637,12 +19736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19706,12 +19805,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -19775,12 +19874,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19844,12 +19943,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -19913,13 +20012,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -19983,12 +20082,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20052,12 +20151,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -20121,12 +20220,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20190,12 +20289,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20259,12 +20358,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -20328,12 +20427,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20397,12 +20496,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20466,12 +20565,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -20535,12 +20634,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20604,12 +20703,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20673,13 +20772,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B115" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -20743,12 +20842,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -20812,12 +20911,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -20881,12 +20980,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -20950,12 +21049,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21019,12 +21118,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21088,12 +21187,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21157,12 +21256,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21226,8 +21325,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21257,7 +21356,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21287,7 +21386,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21317,7 +21416,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21347,7 +21446,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21377,7 +21476,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21407,7 +21506,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21437,7 +21536,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21467,7 +21566,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21497,7 +21596,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21527,7 +21626,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21557,7 +21656,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21587,7 +21686,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21617,7 +21716,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21647,7 +21746,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21677,7 +21776,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -21707,7 +21806,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
